--- a/Result/profitability/6026.xlsx
+++ b/Result/profitability/6026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM62"/>
+  <dimension ref="A1:AM63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,7 +657,7 @@
         <v>-0.11</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2237500000000001</v>
+        <v>0.3500000000000001</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -754,7 +754,7 @@
         <v>-0.74</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1312500000000001</v>
+        <v>0.2450000000000001</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -861,7 +861,7 @@
         <v>-0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1125000000000001</v>
+        <v>0.2275000000000001</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -968,11 +968,11 @@
         <v>0.12</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1162500000000001</v>
+        <v>0.2487500000000001</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1073,7 +1073,7 @@
         <v>-0.54</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05500000000000006</v>
+        <v>0.09875000000000006</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1186,7 +1186,7 @@
         <v>0.71</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06125000000000005</v>
+        <v>0.05875000000000008</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -7750,6 +7750,127 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>6026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>703</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="n">
+        <v>96.27</v>
+      </c>
+      <c r="G63" t="n">
+        <v>482</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>68.48%</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="n">
+        <v>448</v>
+      </c>
+      <c r="K63" t="n">
+        <v>400</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.3637500000000001</v>
+      </c>
+      <c r="N63" t="n">
+        <v>90.005</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="X63" t="n">
+        <v>13.42857142857143</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>7.109999999999999</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0.07974427994616429</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>-21.2</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>14.23999999999999</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.1735950262099231</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK63" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
